--- a/docs/Register-SWI-203.xlsx
+++ b/docs/Register-SWI-203.xlsx
@@ -630,7 +630,7 @@
         <v>6</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MM-4034-033-OR-03-SWI-PRO-MET-203-001-Plant-Survey-Planning-Permitting-and-Execution-RevA.docx</t>
+          <t>SWI-PRO-MET-203-001-Plant-Survey-Planning-Permitting-and-Execution-RevA.docx</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
         <v>5</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MM-4034-033-OR-03-SWI-PRO-MET-203-002-Slurry-Flow-Density-and-Tonnage-Verification-Survey-RevA.docx</t>
+          <t>SWI-PRO-MET-203-002-Slurry-Flow-Density-and-Tonnage-Verification-Survey-RevA.docx</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MM-4034-033-OR-03-SWI-PRO-MET-203-003-Screen-and-Cyclone-Performance-Survey---Size-Split-Determination-RevA.docx</t>
+          <t>SWI-PRO-MET-203-003-Screen-and-Cyclone-Performance-Survey---Size-Split-Determination-RevA.docx</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         <v>5</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MM-4034-033-OR-03-SWI-PRO-MET-203-004-Residence-Time-and-Tracer-Test-on-Leach-and-Adsorption-Trains-RevA.docx</t>
+          <t>SWI-PRO-MET-203-004-Residence-Time-and-Tracer-Test-on-Leach-and-Adsorption-Trains-RevA.docx</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MM-4034-033-OR-03-SWI-PRO-MET-203-005-Leach-and-CIL-Profile-Survey---Tank-by-Tank-Gold-and-Cyanide-Profi-RevA.docx</t>
+          <t>SWI-PRO-MET-203-005-Leach-and-CIL-Profile-Survey---Tank-by-Tank-Gold-and-Cyanide-Profi-RevA.docx</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
         <v>5</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MM-4034-033-OR-03-SWI-PRO-MET-203-006-Adsorption-Profile-Survey---Metal-and-Cyanide-Resin-Circuits-RevA.docx</t>
+          <t>SWI-PRO-MET-203-006-Adsorption-Profile-Survey---Metal-and-Cyanide-Resin-Circuits-RevA.docx</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MM-4034-033-OR-03-SWI-PRO-MET-203-007-Thickener-Performance-Survey---Flux-Bed-Level-and-Flocculant-Respo-RevA.docx</t>
+          <t>SWI-PRO-MET-203-007-Thickener-Performance-Survey---Flux-Bed-Level-and-Flocculant-Respo-RevA.docx</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MM-4034-033-OR-03-SWI-PRO-MET-203-008-Elution-and-Electrowinning-Batch-Performance-Assessment-RevA.docx</t>
+          <t>SWI-PRO-MET-203-008-Elution-and-Electrowinning-Batch-Performance-Assessment-RevA.docx</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MM-4034-033-OR-03-SWI-PRO-MET-203-009-Reagent-Dosing-Verification-and-Dosing-Pump-Calibration-Check-RevA.docx</t>
+          <t>SWI-PRO-MET-203-009-Reagent-Dosing-Verification-and-Dosing-Pump-Calibration-Check-RevA.docx</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MM-4034-033-OR-03-SWI-PRO-MET-203-010-Interstage-and-Safety-Screen-Efficiency-Check-and-Loss-Quantificat-RevA.docx</t>
+          <t>SWI-PRO-MET-203-010-Interstage-and-Safety-Screen-Efficiency-Check-and-Loss-Quantificat-RevA.docx</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MM-4034-033-OR-03-SWI-PRO-MET-203-011-Carbon-and-Resin-Loss-Quantification-Survey-RevA.docx</t>
+          <t>SWI-PRO-MET-203-011-Carbon-and-Resin-Loss-Quantification-Survey-RevA.docx</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MM-4034-033-OR-03-SWI-PRO-MET-203-012-Oxygen-Utilisation-and-Sparger-Performance-Survey-RevA.docx</t>
+          <t>SWI-PRO-MET-203-012-Oxygen-Utilisation-and-Sparger-Performance-Survey-RevA.docx</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -1691,13 +1691,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Referensi register: HM-MMM-WHS-REG-XXX-R00-SWI-SWMS, tab SWI-MET.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
